--- a/artfynd/A 14787-2026 artfynd.xlsx
+++ b/artfynd/A 14787-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132923528</v>
+        <v>132926918</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582287</v>
+        <v>582483</v>
       </c>
       <c r="R2" t="n">
-        <v>7043969</v>
+        <v>7043876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132926918</v>
+        <v>132926854</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582483</v>
+        <v>582450</v>
       </c>
       <c r="R3" t="n">
-        <v>7043876</v>
+        <v>7043889</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132926854</v>
+        <v>132923528</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582450</v>
+        <v>582287</v>
       </c>
       <c r="R4" t="n">
-        <v>7043889</v>
+        <v>7043969</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132926766</v>
+        <v>132925440</v>
       </c>
       <c r="B9" t="n">
-        <v>83181</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582430</v>
+        <v>582314</v>
       </c>
       <c r="R9" t="n">
-        <v>7043874</v>
+        <v>7043846</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132926678</v>
+        <v>132925090</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,34 +1566,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582433</v>
+        <v>582199</v>
       </c>
       <c r="R10" t="n">
-        <v>7043867</v>
+        <v>7043873</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1620,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1640,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132928047</v>
+        <v>132927178</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,37 +1683,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582557</v>
+        <v>582507</v>
       </c>
       <c r="R11" t="n">
-        <v>7043908</v>
+        <v>7043843</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1757,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132925262</v>
+        <v>132926766</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582260</v>
+        <v>582430</v>
       </c>
       <c r="R12" t="n">
-        <v>7043863</v>
+        <v>7043874</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132923551</v>
+        <v>132926678</v>
       </c>
       <c r="B13" t="n">
         <v>91918</v>
@@ -1906,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582302</v>
+        <v>582433</v>
       </c>
       <c r="R13" t="n">
-        <v>7043990</v>
+        <v>7043867</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,22 +1991,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132919070</v>
+        <v>132928047</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582550</v>
+        <v>582557</v>
       </c>
       <c r="R14" t="n">
-        <v>7043815</v>
+        <v>7043908</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132925440</v>
+        <v>132925262</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,21 +2121,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2120,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582314</v>
+        <v>582260</v>
       </c>
       <c r="R15" t="n">
-        <v>7043846</v>
+        <v>7043863</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2217,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132925090</v>
+        <v>132923551</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,42 +2228,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582199</v>
+        <v>582302</v>
       </c>
       <c r="R16" t="n">
-        <v>7043873</v>
+        <v>7043990</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,7 +2287,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,12 +2297,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,22 +2312,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132927178</v>
+        <v>132919070</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,39 +2335,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582507</v>
+        <v>582550</v>
       </c>
       <c r="R17" t="n">
-        <v>7043843</v>
+        <v>7043815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2394,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,12 +2404,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132924051</v>
+        <v>132924276</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,21 +2558,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582272</v>
+        <v>582265</v>
       </c>
       <c r="R19" t="n">
-        <v>7044012</v>
+        <v>7044007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132919816</v>
+        <v>132926159</v>
       </c>
       <c r="B20" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582579</v>
+        <v>582393</v>
       </c>
       <c r="R20" t="n">
-        <v>7043890</v>
+        <v>7043857</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132924276</v>
+        <v>132924051</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,21 +2772,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582265</v>
+        <v>582272</v>
       </c>
       <c r="R21" t="n">
-        <v>7044007</v>
+        <v>7044012</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132926159</v>
+        <v>132919816</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,21 +2879,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582393</v>
+        <v>582579</v>
       </c>
       <c r="R22" t="n">
-        <v>7043857</v>
+        <v>7043890</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132923635</v>
+        <v>132920346</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>57136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,16 +2986,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3006,7 +3006,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582306</v>
+        <v>582529</v>
       </c>
       <c r="R23" t="n">
-        <v>7043991</v>
+        <v>7043897</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,12 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3080,22 +3075,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132920346</v>
+        <v>132923635</v>
       </c>
       <c r="B24" t="n">
-        <v>57136</v>
+        <v>57958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,16 +3098,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3123,7 +3118,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3132,13 +3127,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582529</v>
+        <v>582306</v>
       </c>
       <c r="R24" t="n">
-        <v>7043897</v>
+        <v>7043991</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3167,7 +3162,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3177,7 +3172,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3192,61 +3192,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132923509</v>
+        <v>132920356</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582304</v>
+        <v>582532</v>
       </c>
       <c r="R25" t="n">
-        <v>7043964</v>
+        <v>7043892</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,7 +3274,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3288,7 +3284,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3315,45 +3311,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132920356</v>
+        <v>132923509</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582532</v>
+        <v>582304</v>
       </c>
       <c r="R26" t="n">
-        <v>7043892</v>
+        <v>7043964</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,10 +3422,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132922973</v>
+        <v>132919032</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3433,34 +3433,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582320</v>
+        <v>582546</v>
       </c>
       <c r="R27" t="n">
-        <v>7043917</v>
+        <v>7043836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3497,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3502,7 +3507,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3529,45 +3539,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132922379</v>
+        <v>132919891</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582397</v>
+        <v>582574</v>
       </c>
       <c r="R28" t="n">
-        <v>7043879</v>
+        <v>7043884</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,7 +3613,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3609,7 +3623,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,7 +3650,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132925362</v>
+        <v>132922973</v>
       </c>
       <c r="B29" t="n">
         <v>79333</v>
@@ -3671,10 +3685,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582302</v>
+        <v>582320</v>
       </c>
       <c r="R29" t="n">
-        <v>7043849</v>
+        <v>7043917</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3716,7 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3743,49 +3757,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132919891</v>
+        <v>132922379</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582574</v>
+        <v>582397</v>
       </c>
       <c r="R30" t="n">
-        <v>7043884</v>
+        <v>7043879</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,7 +3827,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3827,7 +3837,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3854,10 +3864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132919032</v>
+        <v>132925362</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3865,39 +3875,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582546</v>
+        <v>582302</v>
       </c>
       <c r="R31" t="n">
-        <v>7043836</v>
+        <v>7043849</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3929,7 +3934,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3939,12 +3944,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132920065</v>
+        <v>132926412</v>
       </c>
       <c r="B32" t="n">
-        <v>91939</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,34 +3982,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582565</v>
+        <v>582422</v>
       </c>
       <c r="R32" t="n">
-        <v>7043895</v>
+        <v>7043879</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4041,7 +4046,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4056,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,10 +4088,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132925222</v>
+        <v>132920065</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>91939</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4089,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,13 +4123,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582250</v>
+        <v>582565</v>
       </c>
       <c r="R33" t="n">
-        <v>7043869</v>
+        <v>7043895</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4148,7 +4158,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4168,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,22 +4183,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132926412</v>
+        <v>132925222</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,42 +4206,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582422</v>
+        <v>582250</v>
       </c>
       <c r="R34" t="n">
-        <v>7043879</v>
+        <v>7043869</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4260,7 +4265,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4270,12 +4275,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4290,12 +4290,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4874,53 +4874,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132919043</v>
+        <v>132926154</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>92290</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582561</v>
+        <v>582384</v>
       </c>
       <c r="R40" t="n">
-        <v>7043822</v>
+        <v>7043861</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4949,7 +4944,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4959,12 +4954,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4979,22 +4969,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132926421</v>
+        <v>132919360</v>
       </c>
       <c r="B41" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5002,42 +4992,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582415</v>
+        <v>582533</v>
       </c>
       <c r="R41" t="n">
-        <v>7043878</v>
+        <v>7043840</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5066,7 +5051,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5076,12 +5061,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,22 +5076,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132919076</v>
+        <v>132920570</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,42 +5099,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582558</v>
+        <v>582496</v>
       </c>
       <c r="R42" t="n">
-        <v>7043820</v>
+        <v>7043918</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5183,7 +5158,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5193,12 +5168,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5213,22 +5183,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132919360</v>
+        <v>132919043</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5236,34 +5206,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582533</v>
+        <v>582561</v>
       </c>
       <c r="R43" t="n">
-        <v>7043840</v>
+        <v>7043822</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5295,7 +5270,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5305,7 +5280,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5332,10 +5312,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132920570</v>
+        <v>132926421</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,34 +5323,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582496</v>
+        <v>582415</v>
       </c>
       <c r="R44" t="n">
-        <v>7043918</v>
+        <v>7043878</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5402,7 +5387,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5412,7 +5397,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5439,48 +5429,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132926154</v>
+        <v>132919076</v>
       </c>
       <c r="B45" t="n">
-        <v>92290</v>
+        <v>57958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582384</v>
+        <v>582558</v>
       </c>
       <c r="R45" t="n">
-        <v>7043861</v>
+        <v>7043820</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5509,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5519,7 +5514,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5534,12 +5534,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5653,37 +5653,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132925338</v>
+        <v>132925842</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5692,13 +5693,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582282</v>
+        <v>582336</v>
       </c>
       <c r="R47" t="n">
-        <v>7043849</v>
+        <v>7043843</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5727,7 +5728,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5738,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,50 +5758,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132925842</v>
+        <v>132925338</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5804,13 +5809,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582336</v>
+        <v>582282</v>
       </c>
       <c r="R48" t="n">
-        <v>7043843</v>
+        <v>7043849</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5839,7 +5844,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5849,12 +5854,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:43</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5869,12 +5869,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132925307</v>
+        <v>132926094</v>
       </c>
       <c r="B61" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,21 +7236,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582282</v>
+        <v>582388</v>
       </c>
       <c r="R61" t="n">
-        <v>7043846</v>
+        <v>7043864</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7332,7 +7332,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132926094</v>
+        <v>132926171</v>
       </c>
       <c r="B62" t="n">
         <v>92217</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582388</v>
+        <v>582386</v>
       </c>
       <c r="R62" t="n">
-        <v>7043864</v>
+        <v>7043846</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7439,10 +7439,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132926171</v>
+        <v>132925307</v>
       </c>
       <c r="B63" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582386</v>
+        <v>582282</v>
       </c>
       <c r="R63" t="n">
         <v>7043846</v>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7546,48 +7546,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132920807</v>
+        <v>132926466</v>
       </c>
       <c r="B64" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582487</v>
+        <v>582411</v>
       </c>
       <c r="R64" t="n">
-        <v>7043925</v>
+        <v>7043872</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7616,7 +7620,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7626,7 +7630,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7641,19 +7645,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132928237</v>
+        <v>132920807</v>
       </c>
       <c r="B65" t="n">
         <v>80438</v>
@@ -7688,10 +7692,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582565</v>
+        <v>582487</v>
       </c>
       <c r="R65" t="n">
-        <v>7043970</v>
+        <v>7043925</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7723,7 +7727,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7733,7 +7737,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7760,52 +7764,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132926466</v>
+        <v>132928237</v>
       </c>
       <c r="B66" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582411</v>
+        <v>582565</v>
       </c>
       <c r="R66" t="n">
-        <v>7043872</v>
+        <v>7043970</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7859,12 +7859,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8105,37 +8105,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132921030</v>
+        <v>132920433</v>
       </c>
       <c r="B69" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8144,13 +8145,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>582465</v>
+        <v>582522</v>
       </c>
       <c r="R69" t="n">
-        <v>7043920</v>
+        <v>7043904</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8179,7 +8180,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8189,7 +8190,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8204,49 +8210,50 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132920457</v>
+        <v>132925210</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8255,10 +8262,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>582512</v>
+        <v>582246</v>
       </c>
       <c r="R70" t="n">
-        <v>7043909</v>
+        <v>7043866</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8290,7 +8297,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8300,7 +8307,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8327,7 +8339,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132920433</v>
+        <v>132924803</v>
       </c>
       <c r="B71" t="n">
         <v>57958</v>
@@ -8367,13 +8379,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>582522</v>
+        <v>582184</v>
       </c>
       <c r="R71" t="n">
-        <v>7043904</v>
+        <v>7043908</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8402,7 +8414,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8412,7 +8424,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8432,50 +8444,49 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132925210</v>
+        <v>132921030</v>
       </c>
       <c r="B72" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8484,10 +8495,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>582246</v>
+        <v>582465</v>
       </c>
       <c r="R72" t="n">
-        <v>7043866</v>
+        <v>7043920</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8519,7 +8530,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8529,12 +8540,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8561,38 +8567,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132924803</v>
+        <v>132920457</v>
       </c>
       <c r="B73" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8601,10 +8606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>582184</v>
+        <v>582512</v>
       </c>
       <c r="R73" t="n">
-        <v>7043908</v>
+        <v>7043909</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8636,7 +8641,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8646,12 +8651,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 14787-2026 artfynd.xlsx
+++ b/artfynd/A 14787-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132926918</v>
+        <v>132923528</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582483</v>
+        <v>582287</v>
       </c>
       <c r="R2" t="n">
-        <v>7043876</v>
+        <v>7043969</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132926854</v>
+        <v>132926918</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582450</v>
+        <v>582483</v>
       </c>
       <c r="R3" t="n">
-        <v>7043889</v>
+        <v>7043876</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132923528</v>
+        <v>132926854</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582287</v>
+        <v>582450</v>
       </c>
       <c r="R4" t="n">
-        <v>7043969</v>
+        <v>7043889</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132925440</v>
+        <v>132926678</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582314</v>
+        <v>582433</v>
       </c>
       <c r="R9" t="n">
-        <v>7043846</v>
+        <v>7043867</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,12 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,22 +1538,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132925090</v>
+        <v>132928047</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,42 +1561,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582199</v>
+        <v>582557</v>
       </c>
       <c r="R10" t="n">
-        <v>7043873</v>
+        <v>7043908</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,12 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,22 +1645,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132927178</v>
+        <v>132925262</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,39 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582507</v>
+        <v>582260</v>
       </c>
       <c r="R11" t="n">
-        <v>7043843</v>
+        <v>7043863</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,12 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132926766</v>
+        <v>132923551</v>
       </c>
       <c r="B12" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582430</v>
+        <v>582302</v>
       </c>
       <c r="R12" t="n">
-        <v>7043874</v>
+        <v>7043990</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132926678</v>
+        <v>132919070</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1906,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582433</v>
+        <v>582550</v>
       </c>
       <c r="R13" t="n">
-        <v>7043867</v>
+        <v>7043815</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,22 +1966,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132928047</v>
+        <v>132926766</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +1989,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2013,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582557</v>
+        <v>582430</v>
       </c>
       <c r="R14" t="n">
-        <v>7043908</v>
+        <v>7043874</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132925262</v>
+        <v>132925440</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,21 +2096,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2145,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582260</v>
+        <v>582314</v>
       </c>
       <c r="R15" t="n">
-        <v>7043863</v>
+        <v>7043846</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2155,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2165,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132923551</v>
+        <v>132925090</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,37 +2208,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582302</v>
+        <v>582199</v>
       </c>
       <c r="R16" t="n">
-        <v>7043990</v>
+        <v>7043873</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2287,7 +2272,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2297,7 +2282,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,22 +2302,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132919070</v>
+        <v>132927178</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,34 +2325,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582550</v>
+        <v>582507</v>
       </c>
       <c r="R17" t="n">
-        <v>7043815</v>
+        <v>7043843</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2404,7 +2399,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132924051</v>
+        <v>132923635</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,34 +2772,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582272</v>
+        <v>582306</v>
       </c>
       <c r="R21" t="n">
-        <v>7044012</v>
+        <v>7043991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,7 +2836,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2841,7 +2846,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132919816</v>
+        <v>132924051</v>
       </c>
       <c r="B22" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,21 +2889,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2903,10 +2913,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582579</v>
+        <v>582272</v>
       </c>
       <c r="R22" t="n">
-        <v>7043890</v>
+        <v>7044012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,7 +2948,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2948,7 +2958,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,10 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132920346</v>
+        <v>132919816</v>
       </c>
       <c r="B23" t="n">
-        <v>57136</v>
+        <v>80438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,42 +2996,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582529</v>
+        <v>582579</v>
       </c>
       <c r="R23" t="n">
-        <v>7043897</v>
+        <v>7043890</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3055,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3065,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,22 +3080,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132923635</v>
+        <v>132920346</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>57136</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3098,16 +3103,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3118,7 +3123,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3127,13 +3132,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582306</v>
+        <v>582529</v>
       </c>
       <c r="R24" t="n">
-        <v>7043991</v>
+        <v>7043897</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3162,7 +3167,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3172,12 +3177,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3192,57 +3192,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132920356</v>
+        <v>132923509</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582532</v>
+        <v>582304</v>
       </c>
       <c r="R25" t="n">
-        <v>7043892</v>
+        <v>7043964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3274,7 +3278,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3284,7 +3288,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3311,49 +3315,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132923509</v>
+        <v>132920356</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582304</v>
+        <v>582532</v>
       </c>
       <c r="R26" t="n">
-        <v>7043964</v>
+        <v>7043892</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,10 +3422,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132919032</v>
+        <v>132922973</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3433,39 +3433,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582546</v>
+        <v>582320</v>
       </c>
       <c r="R27" t="n">
-        <v>7043836</v>
+        <v>7043917</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,7 +3492,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3507,12 +3502,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3539,49 +3529,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132919891</v>
+        <v>132922379</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582574</v>
+        <v>582397</v>
       </c>
       <c r="R28" t="n">
-        <v>7043884</v>
+        <v>7043879</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3613,7 +3599,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3623,7 +3609,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,7 +3636,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132922973</v>
+        <v>132925362</v>
       </c>
       <c r="B29" t="n">
         <v>79333</v>
@@ -3685,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582320</v>
+        <v>582302</v>
       </c>
       <c r="R29" t="n">
-        <v>7043917</v>
+        <v>7043849</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,7 +3706,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3730,7 +3716,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3757,10 +3743,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132922379</v>
+        <v>132919032</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,34 +3754,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582397</v>
+        <v>582546</v>
       </c>
       <c r="R30" t="n">
-        <v>7043879</v>
+        <v>7043836</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3827,7 +3818,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3837,7 +3828,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,45 +3860,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132925362</v>
+        <v>132919891</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582302</v>
+        <v>582574</v>
       </c>
       <c r="R31" t="n">
-        <v>7043849</v>
+        <v>7043884</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132926412</v>
+        <v>132920065</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>91939</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,39 +3982,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582422</v>
+        <v>582565</v>
       </c>
       <c r="R32" t="n">
-        <v>7043879</v>
+        <v>7043895</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4046,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4056,12 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,10 +4078,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132920065</v>
+        <v>132925222</v>
       </c>
       <c r="B33" t="n">
-        <v>91939</v>
+        <v>79333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4099,21 +4089,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,13 +4113,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582565</v>
+        <v>582250</v>
       </c>
       <c r="R33" t="n">
-        <v>7043895</v>
+        <v>7043869</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4158,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4168,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4183,57 +4173,61 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132925222</v>
+        <v>132923147</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582250</v>
+        <v>582359</v>
       </c>
       <c r="R34" t="n">
-        <v>7043869</v>
+        <v>7043899</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4265,7 +4259,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4275,7 +4269,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4302,37 +4296,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132923147</v>
+        <v>132926412</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4341,13 +4336,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582359</v>
+        <v>582422</v>
       </c>
       <c r="R35" t="n">
-        <v>7043899</v>
+        <v>7043879</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4376,7 +4371,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4386,7 +4381,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,12 +4401,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4874,32 +4874,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132926154</v>
+        <v>132919360</v>
       </c>
       <c r="B40" t="n">
-        <v>92290</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582384</v>
+        <v>582533</v>
       </c>
       <c r="R40" t="n">
-        <v>7043861</v>
+        <v>7043840</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4969,44 +4969,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132919360</v>
+        <v>132926154</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>92290</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5016,13 +5016,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582533</v>
+        <v>582384</v>
       </c>
       <c r="R41" t="n">
-        <v>7043840</v>
+        <v>7043861</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5076,12 +5076,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132919337</v>
+        <v>132920535</v>
       </c>
       <c r="B53" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,42 +6330,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582540</v>
+        <v>582516</v>
       </c>
       <c r="R53" t="n">
-        <v>7043843</v>
+        <v>7043923</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6394,7 +6389,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6404,12 +6399,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6424,19 +6414,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132926178</v>
+        <v>132919337</v>
       </c>
       <c r="B54" t="n">
         <v>57958</v>
@@ -6476,10 +6466,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582395</v>
+        <v>582540</v>
       </c>
       <c r="R54" t="n">
-        <v>7043859</v>
+        <v>7043843</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6511,7 +6501,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6521,7 +6511,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6553,7 +6543,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132926237</v>
+        <v>132926178</v>
       </c>
       <c r="B55" t="n">
         <v>57958</v>
@@ -6584,7 +6574,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6593,10 +6583,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582399</v>
+        <v>582395</v>
       </c>
       <c r="R55" t="n">
-        <v>7043854</v>
+        <v>7043859</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6628,7 +6618,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6638,7 +6628,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6670,10 +6660,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132920535</v>
+        <v>132926237</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6681,37 +6671,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582516</v>
+        <v>582399</v>
       </c>
       <c r="R56" t="n">
-        <v>7043923</v>
+        <v>7043854</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6740,7 +6735,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6750,7 +6745,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6765,12 +6765,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132925942</v>
+        <v>132927484</v>
       </c>
       <c r="B58" t="n">
-        <v>91939</v>
+        <v>57958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6895,37 +6895,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582341</v>
+        <v>582555</v>
       </c>
       <c r="R58" t="n">
-        <v>7043851</v>
+        <v>7043817</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6954,7 +6959,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6964,7 +6969,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6979,19 +6989,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132927484</v>
+        <v>132920331</v>
       </c>
       <c r="B59" t="n">
         <v>57958</v>
@@ -7022,7 +7032,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7031,13 +7041,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582555</v>
+        <v>582528</v>
       </c>
       <c r="R59" t="n">
-        <v>7043817</v>
+        <v>7043891</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7066,7 +7076,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7076,7 +7086,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7096,22 +7106,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132920331</v>
+        <v>132925942</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>91939</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7119,39 +7129,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>582528</v>
+        <v>582341</v>
       </c>
       <c r="R60" t="n">
-        <v>7043891</v>
+        <v>7043851</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7183,7 +7188,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7193,12 +7198,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7225,10 +7225,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132926094</v>
+        <v>132920807</v>
       </c>
       <c r="B61" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,21 +7236,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582388</v>
+        <v>582487</v>
       </c>
       <c r="R61" t="n">
-        <v>7043864</v>
+        <v>7043925</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7320,22 +7320,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132926171</v>
+        <v>132928237</v>
       </c>
       <c r="B62" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,21 +7343,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582386</v>
+        <v>582565</v>
       </c>
       <c r="R62" t="n">
-        <v>7043846</v>
+        <v>7043970</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7427,22 +7427,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132925307</v>
+        <v>132926094</v>
       </c>
       <c r="B63" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582282</v>
+        <v>582388</v>
       </c>
       <c r="R63" t="n">
-        <v>7043846</v>
+        <v>7043864</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7546,49 +7546,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132926466</v>
+        <v>132926171</v>
       </c>
       <c r="B64" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582411</v>
+        <v>582386</v>
       </c>
       <c r="R64" t="n">
-        <v>7043872</v>
+        <v>7043846</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7620,7 +7616,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7630,7 +7626,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7657,10 +7653,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132920807</v>
+        <v>132925307</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7668,21 +7664,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7692,13 +7688,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582487</v>
+        <v>582282</v>
       </c>
       <c r="R65" t="n">
-        <v>7043925</v>
+        <v>7043846</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7727,7 +7723,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7737,7 +7733,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7752,60 +7748,64 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132928237</v>
+        <v>132926466</v>
       </c>
       <c r="B66" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582565</v>
+        <v>582411</v>
       </c>
       <c r="R66" t="n">
-        <v>7043970</v>
+        <v>7043872</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7859,12 +7859,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14787-2026 artfynd.xlsx
+++ b/artfynd/A 14787-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132923528</v>
+        <v>132926918</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582287</v>
+        <v>582483</v>
       </c>
       <c r="R2" t="n">
-        <v>7043969</v>
+        <v>7043876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132926918</v>
+        <v>132923528</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582483</v>
+        <v>582287</v>
       </c>
       <c r="R3" t="n">
-        <v>7043876</v>
+        <v>7043969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132926678</v>
+        <v>132925440</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582433</v>
+        <v>582314</v>
       </c>
       <c r="R9" t="n">
-        <v>7043867</v>
+        <v>7043846</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,22 +1543,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132928047</v>
+        <v>132925090</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,37 +1566,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582557</v>
+        <v>582199</v>
       </c>
       <c r="R10" t="n">
-        <v>7043908</v>
+        <v>7043873</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1640,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,22 +1660,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132925262</v>
+        <v>132927178</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,34 +1683,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582260</v>
+        <v>582507</v>
       </c>
       <c r="R11" t="n">
-        <v>7043863</v>
+        <v>7043843</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1757,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132919070</v>
+        <v>132928047</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582550</v>
+        <v>582557</v>
       </c>
       <c r="R13" t="n">
-        <v>7043815</v>
+        <v>7043908</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132926766</v>
+        <v>132926678</v>
       </c>
       <c r="B14" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582430</v>
+        <v>582433</v>
       </c>
       <c r="R14" t="n">
-        <v>7043874</v>
+        <v>7043867</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,22 +2098,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132925440</v>
+        <v>132926766</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>83181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,21 +2121,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2120,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582314</v>
+        <v>582430</v>
       </c>
       <c r="R15" t="n">
-        <v>7043846</v>
+        <v>7043874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2165,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2217,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132925090</v>
+        <v>132925262</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,42 +2228,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582199</v>
+        <v>582260</v>
       </c>
       <c r="R16" t="n">
-        <v>7043873</v>
+        <v>7043863</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,7 +2287,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,12 +2297,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,22 +2312,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132927178</v>
+        <v>132919070</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,39 +2335,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582507</v>
+        <v>582550</v>
       </c>
       <c r="R17" t="n">
-        <v>7043843</v>
+        <v>7043815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2394,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,12 +2404,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,7 +2547,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132924276</v>
+        <v>132926159</v>
       </c>
       <c r="B19" t="n">
         <v>91918</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582265</v>
+        <v>582393</v>
       </c>
       <c r="R19" t="n">
-        <v>7044007</v>
+        <v>7043857</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,7 +2654,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132926159</v>
+        <v>132924276</v>
       </c>
       <c r="B20" t="n">
         <v>91918</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582393</v>
+        <v>582265</v>
       </c>
       <c r="R20" t="n">
-        <v>7043857</v>
+        <v>7044007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132923635</v>
+        <v>132924051</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,39 +2772,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582306</v>
+        <v>582272</v>
       </c>
       <c r="R21" t="n">
-        <v>7043991</v>
+        <v>7044012</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,7 +2831,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,12 +2841,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2878,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132924051</v>
+        <v>132919816</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2889,21 +2879,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2913,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582272</v>
+        <v>582579</v>
       </c>
       <c r="R22" t="n">
-        <v>7044012</v>
+        <v>7043890</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,7 +2938,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2958,7 +2948,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132919816</v>
+        <v>132920346</v>
       </c>
       <c r="B23" t="n">
-        <v>80438</v>
+        <v>57136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,37 +2986,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582579</v>
+        <v>582529</v>
       </c>
       <c r="R23" t="n">
-        <v>7043890</v>
+        <v>7043897</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3055,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3065,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3080,22 +3075,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132920346</v>
+        <v>132923635</v>
       </c>
       <c r="B24" t="n">
-        <v>57136</v>
+        <v>57958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,16 +3098,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3123,7 +3118,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3132,13 +3127,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582529</v>
+        <v>582306</v>
       </c>
       <c r="R24" t="n">
-        <v>7043897</v>
+        <v>7043991</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3167,7 +3162,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3177,7 +3172,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3192,61 +3192,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132923509</v>
+        <v>132920356</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582304</v>
+        <v>582532</v>
       </c>
       <c r="R25" t="n">
-        <v>7043964</v>
+        <v>7043892</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,7 +3274,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3288,7 +3284,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3315,45 +3311,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132920356</v>
+        <v>132923509</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582532</v>
+        <v>582304</v>
       </c>
       <c r="R26" t="n">
-        <v>7043892</v>
+        <v>7043964</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3743,38 +3743,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132919032</v>
+        <v>132919891</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3783,10 +3782,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582546</v>
+        <v>582574</v>
       </c>
       <c r="R30" t="n">
-        <v>7043836</v>
+        <v>7043884</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3818,7 +3817,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3828,12 +3827,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3860,37 +3854,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132919891</v>
+        <v>132919032</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3899,10 +3894,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582574</v>
+        <v>582546</v>
       </c>
       <c r="R31" t="n">
-        <v>7043884</v>
+        <v>7043836</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,7 +3929,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3944,7 +3939,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4185,37 +4185,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132923147</v>
+        <v>132926412</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4224,13 +4225,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582359</v>
+        <v>582422</v>
       </c>
       <c r="R34" t="n">
-        <v>7043899</v>
+        <v>7043879</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4259,7 +4260,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4269,7 +4270,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4284,50 +4290,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132926412</v>
+        <v>132923147</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4336,13 +4341,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582422</v>
+        <v>582359</v>
       </c>
       <c r="R35" t="n">
-        <v>7043879</v>
+        <v>7043899</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4371,7 +4376,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4381,12 +4386,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,12 +4401,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4874,32 +4874,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132919360</v>
+        <v>132926154</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>92290</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582533</v>
+        <v>582384</v>
       </c>
       <c r="R40" t="n">
-        <v>7043840</v>
+        <v>7043861</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4969,44 +4969,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132926154</v>
+        <v>132919360</v>
       </c>
       <c r="B41" t="n">
-        <v>92290</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5016,13 +5016,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582384</v>
+        <v>582533</v>
       </c>
       <c r="R41" t="n">
-        <v>7043861</v>
+        <v>7043840</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5076,12 +5076,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132927050</v>
+        <v>132925842</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5557,37 +5557,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582494</v>
+        <v>582336</v>
       </c>
       <c r="R46" t="n">
-        <v>7043853</v>
+        <v>7043843</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5616,7 +5621,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5626,7 +5631,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5641,22 +5651,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132925842</v>
+        <v>132927050</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,42 +5674,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582336</v>
+        <v>582494</v>
       </c>
       <c r="R47" t="n">
-        <v>7043843</v>
+        <v>7043853</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5728,7 +5733,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5738,12 +5743,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:43</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5758,12 +5758,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132924903</v>
+        <v>132920535</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>582175</v>
+        <v>582516</v>
       </c>
       <c r="R51" t="n">
-        <v>7043894</v>
+        <v>7043923</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6212,7 +6212,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132926960</v>
+        <v>132924903</v>
       </c>
       <c r="B52" t="n">
         <v>79333</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582484</v>
+        <v>582175</v>
       </c>
       <c r="R52" t="n">
-        <v>7043864</v>
+        <v>7043894</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6319,10 +6319,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132920535</v>
+        <v>132926960</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582516</v>
+        <v>582484</v>
       </c>
       <c r="R53" t="n">
-        <v>7043923</v>
+        <v>7043864</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6884,10 +6884,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132927484</v>
+        <v>132925942</v>
       </c>
       <c r="B58" t="n">
-        <v>57958</v>
+        <v>91939</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6895,42 +6895,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582555</v>
+        <v>582341</v>
       </c>
       <c r="R58" t="n">
-        <v>7043817</v>
+        <v>7043851</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6959,7 +6954,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6969,12 +6964,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6989,19 +6979,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132920331</v>
+        <v>132927484</v>
       </c>
       <c r="B59" t="n">
         <v>57958</v>
@@ -7032,7 +7022,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7041,13 +7031,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582528</v>
+        <v>582555</v>
       </c>
       <c r="R59" t="n">
-        <v>7043891</v>
+        <v>7043817</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7076,7 +7066,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7086,7 +7076,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7106,22 +7096,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132925942</v>
+        <v>132920331</v>
       </c>
       <c r="B60" t="n">
-        <v>91939</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7129,34 +7119,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>582341</v>
+        <v>582528</v>
       </c>
       <c r="R60" t="n">
-        <v>7043851</v>
+        <v>7043891</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7188,7 +7183,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7198,7 +7193,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7225,10 +7225,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132920807</v>
+        <v>132925307</v>
       </c>
       <c r="B61" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,21 +7236,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582487</v>
+        <v>582282</v>
       </c>
       <c r="R61" t="n">
-        <v>7043925</v>
+        <v>7043846</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7320,22 +7320,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132928237</v>
+        <v>132926171</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>92217</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,21 +7343,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582565</v>
+        <v>582386</v>
       </c>
       <c r="R62" t="n">
-        <v>7043970</v>
+        <v>7043846</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7427,12 +7427,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132926171</v>
+        <v>132920807</v>
       </c>
       <c r="B64" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582386</v>
+        <v>582487</v>
       </c>
       <c r="R64" t="n">
-        <v>7043846</v>
+        <v>7043925</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7641,22 +7641,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132925307</v>
+        <v>132928237</v>
       </c>
       <c r="B65" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7664,21 +7664,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7688,13 +7688,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582282</v>
+        <v>582565</v>
       </c>
       <c r="R65" t="n">
-        <v>7043846</v>
+        <v>7043970</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7748,12 +7748,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8105,38 +8105,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132920433</v>
+        <v>132921030</v>
       </c>
       <c r="B69" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8145,13 +8144,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>582522</v>
+        <v>582465</v>
       </c>
       <c r="R69" t="n">
-        <v>7043904</v>
+        <v>7043920</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8180,7 +8179,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8190,12 +8189,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8210,50 +8204,49 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132925210</v>
+        <v>132920457</v>
       </c>
       <c r="B70" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8262,10 +8255,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>582246</v>
+        <v>582512</v>
       </c>
       <c r="R70" t="n">
-        <v>7043866</v>
+        <v>7043909</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8297,7 +8290,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8307,12 +8300,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8339,7 +8327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132924803</v>
+        <v>132920433</v>
       </c>
       <c r="B71" t="n">
         <v>57958</v>
@@ -8379,13 +8367,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>582184</v>
+        <v>582522</v>
       </c>
       <c r="R71" t="n">
-        <v>7043908</v>
+        <v>7043904</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8414,7 +8402,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8424,7 +8412,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8444,49 +8432,50 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132921030</v>
+        <v>132925210</v>
       </c>
       <c r="B72" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8495,10 +8484,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>582465</v>
+        <v>582246</v>
       </c>
       <c r="R72" t="n">
-        <v>7043920</v>
+        <v>7043866</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8530,7 +8519,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8540,7 +8529,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8567,37 +8561,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132920457</v>
+        <v>132924803</v>
       </c>
       <c r="B73" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8606,10 +8601,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>582512</v>
+        <v>582184</v>
       </c>
       <c r="R73" t="n">
-        <v>7043909</v>
+        <v>7043908</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8641,7 +8636,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8651,7 +8646,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8678,48 +8678,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132921934</v>
+        <v>132925868</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>582424</v>
+        <v>582341</v>
       </c>
       <c r="R74" t="n">
-        <v>7043909</v>
+        <v>7043829</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8748,7 +8757,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8758,7 +8767,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8773,69 +8782,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132925868</v>
+        <v>132921934</v>
       </c>
       <c r="B75" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>582341</v>
+        <v>582424</v>
       </c>
       <c r="R75" t="n">
-        <v>7043829</v>
+        <v>7043909</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8889,12 +8889,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 14787-2026 artfynd.xlsx
+++ b/artfynd/A 14787-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132926854</v>
+        <v>132925650</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>92593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582450</v>
+        <v>582319</v>
       </c>
       <c r="R2" t="n">
-        <v>7043889</v>
+        <v>7043818</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132926918</v>
+        <v>132920640</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,20 +810,29 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582483</v>
+        <v>582491</v>
       </c>
       <c r="R3" t="n">
-        <v>7043876</v>
+        <v>7043910</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,69 +886,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132924740</v>
+        <v>132925538</v>
       </c>
       <c r="B4" t="n">
-        <v>99140</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582171</v>
+        <v>582316</v>
       </c>
       <c r="R4" t="n">
-        <v>7043917</v>
+        <v>7043839</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132923528</v>
+        <v>132926094</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582287</v>
+        <v>582388</v>
       </c>
       <c r="R5" t="n">
-        <v>7043969</v>
+        <v>7043864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132924676</v>
+        <v>132926171</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582180</v>
+        <v>582386</v>
       </c>
       <c r="R6" t="n">
-        <v>7043920</v>
+        <v>7043846</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,22 +1207,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132925538</v>
+        <v>132926918</v>
       </c>
       <c r="B7" t="n">
-        <v>92227</v>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582316</v>
+        <v>582483</v>
       </c>
       <c r="R7" t="n">
-        <v>7043839</v>
+        <v>7043876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1326,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132926776</v>
+        <v>132920535</v>
       </c>
       <c r="B8" t="n">
-        <v>92300</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582433</v>
+        <v>582516</v>
       </c>
       <c r="R8" t="n">
-        <v>7043867</v>
+        <v>7043923</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,22 +1421,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132925440</v>
+        <v>132920621</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582314</v>
+        <v>582501</v>
       </c>
       <c r="R9" t="n">
-        <v>7043846</v>
+        <v>7043923</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132925090</v>
+        <v>132923551</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,42 +1551,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582199</v>
+        <v>582302</v>
       </c>
       <c r="R10" t="n">
-        <v>7043873</v>
+        <v>7043990</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,12 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,22 +1635,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132927178</v>
+        <v>132924276</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,39 +1658,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582507</v>
+        <v>582265</v>
       </c>
       <c r="R11" t="n">
-        <v>7043843</v>
+        <v>7044007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,12 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132919070</v>
+        <v>132925262</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1765,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582550</v>
+        <v>582260</v>
       </c>
       <c r="R12" t="n">
-        <v>7043815</v>
+        <v>7043863</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,57 +1861,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132923334</v>
+        <v>132925307</v>
       </c>
       <c r="B13" t="n">
-        <v>99140</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582317</v>
+        <v>582282</v>
       </c>
       <c r="R13" t="n">
-        <v>7043947</v>
+        <v>7043846</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,22 +1956,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132926766</v>
+        <v>132926159</v>
       </c>
       <c r="B14" t="n">
-        <v>83183</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,21 +1979,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582430</v>
+        <v>582393</v>
       </c>
       <c r="R14" t="n">
-        <v>7043874</v>
+        <v>7043857</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2092,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,7 +2078,7 @@
         <v>132926678</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2185,7 @@
         <v>132928047</v>
       </c>
       <c r="B16" t="n">
-        <v>91928</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132925262</v>
+        <v>132926766</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>83222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,21 +2300,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2368,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582260</v>
+        <v>582430</v>
       </c>
       <c r="R17" t="n">
-        <v>7043863</v>
+        <v>7043874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2413,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132923551</v>
+        <v>132926154</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>92318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582302</v>
+        <v>582384</v>
       </c>
       <c r="R18" t="n">
-        <v>7043990</v>
+        <v>7043861</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,53 +2503,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132923635</v>
+        <v>132926776</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>92318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582306</v>
+        <v>582433</v>
       </c>
       <c r="R19" t="n">
-        <v>7043991</v>
+        <v>7043867</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2622,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2632,12 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,65 +2598,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132920346</v>
+        <v>132928275</v>
       </c>
       <c r="B20" t="n">
-        <v>57136</v>
+        <v>92199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582529</v>
+        <v>582584</v>
       </c>
       <c r="R20" t="n">
-        <v>7043897</v>
+        <v>7043980</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132924276</v>
+        <v>132920065</v>
       </c>
       <c r="B21" t="n">
-        <v>91928</v>
+        <v>91995</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,21 +2728,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2752,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582265</v>
+        <v>582565</v>
       </c>
       <c r="R21" t="n">
-        <v>7044007</v>
+        <v>7043895</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,22 +2812,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132926159</v>
+        <v>132925942</v>
       </c>
       <c r="B22" t="n">
-        <v>91928</v>
+        <v>91995</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2894,21 +2835,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2918,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582393</v>
+        <v>582341</v>
       </c>
       <c r="R22" t="n">
-        <v>7043857</v>
+        <v>7043851</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2963,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,14 +2931,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132924051</v>
+        <v>132919070</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3025,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582272</v>
+        <v>582550</v>
       </c>
       <c r="R23" t="n">
-        <v>7044012</v>
+        <v>7043815</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3070,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,32 +3038,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132919816</v>
+        <v>132919360</v>
       </c>
       <c r="B24" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3132,13 +3073,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582579</v>
+        <v>582533</v>
       </c>
       <c r="R24" t="n">
-        <v>7043890</v>
+        <v>7043840</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3167,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3177,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3192,12 +3133,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3207,11 +3148,11 @@
         <v>132920356</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3311,10 +3252,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132923509</v>
+        <v>132920570</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,38 +3263,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582304</v>
+        <v>582496</v>
       </c>
       <c r="R26" t="n">
-        <v>7043964</v>
+        <v>7043918</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3395,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,50 +3359,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132919032</v>
+        <v>132921934</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582546</v>
+        <v>582424</v>
       </c>
       <c r="R27" t="n">
-        <v>7043836</v>
+        <v>7043909</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,7 +3429,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3507,12 +3439,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3539,14 +3466,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132922973</v>
+        <v>132922379</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3574,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582320</v>
+        <v>582397</v>
       </c>
       <c r="R28" t="n">
-        <v>7043917</v>
+        <v>7043879</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,7 +3536,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3619,7 +3546,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3646,14 +3573,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132925362</v>
+        <v>132922973</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3681,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582302</v>
+        <v>582320</v>
       </c>
       <c r="R29" t="n">
-        <v>7043849</v>
+        <v>7043917</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3716,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3726,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,14 +3680,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132922379</v>
+        <v>132923528</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3788,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582397</v>
+        <v>582287</v>
       </c>
       <c r="R30" t="n">
-        <v>7043879</v>
+        <v>7043969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3860,10 +3787,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132919891</v>
+        <v>132924051</v>
       </c>
       <c r="B31" t="n">
-        <v>99140</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,38 +3798,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582574</v>
+        <v>582272</v>
       </c>
       <c r="R31" t="n">
-        <v>7043884</v>
+        <v>7044012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3944,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,10 +3894,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132923147</v>
+        <v>132924527</v>
       </c>
       <c r="B32" t="n">
-        <v>99140</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,38 +3905,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582359</v>
+        <v>582219</v>
       </c>
       <c r="R32" t="n">
-        <v>7043899</v>
+        <v>7043974</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4045,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4055,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,50 +4001,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132926412</v>
+        <v>132924676</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582422</v>
+        <v>582180</v>
       </c>
       <c r="R33" t="n">
-        <v>7043879</v>
+        <v>7043920</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4157,7 +4071,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4167,12 +4081,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4199,14 +4108,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132925222</v>
+        <v>132924903</v>
       </c>
       <c r="B34" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4234,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582250</v>
+        <v>582175</v>
       </c>
       <c r="R34" t="n">
-        <v>7043869</v>
+        <v>7043894</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4269,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4279,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4306,32 +4215,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132920065</v>
+        <v>132925222</v>
       </c>
       <c r="B35" t="n">
-        <v>91949</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4341,13 +4250,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582565</v>
+        <v>582250</v>
       </c>
       <c r="R35" t="n">
-        <v>7043895</v>
+        <v>7043869</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4376,7 +4285,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4386,7 +4295,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,22 +4310,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132926033</v>
+        <v>132925362</v>
       </c>
       <c r="B36" t="n">
-        <v>99140</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4424,38 +4333,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582361</v>
+        <v>582302</v>
       </c>
       <c r="R36" t="n">
-        <v>7043841</v>
+        <v>7043849</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4487,7 +4392,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4497,7 +4402,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4524,57 +4429,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132920640</v>
+        <v>132926960</v>
       </c>
       <c r="B37" t="n">
-        <v>92227</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582491</v>
+        <v>582484</v>
       </c>
       <c r="R37" t="n">
-        <v>7043910</v>
+        <v>7043864</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4603,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4613,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4628,62 +4524,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132924726</v>
+        <v>132927050</v>
       </c>
       <c r="B38" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582191</v>
+        <v>582494</v>
       </c>
       <c r="R38" t="n">
-        <v>7043924</v>
+        <v>7043853</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4715,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4725,12 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4757,53 +4643,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132922007</v>
+        <v>132928234</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582415</v>
+        <v>582566</v>
       </c>
       <c r="R39" t="n">
-        <v>7043917</v>
+        <v>7043963</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4832,7 +4713,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4842,12 +4723,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4862,65 +4738,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132919043</v>
+        <v>132928381</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582561</v>
+        <v>582595</v>
       </c>
       <c r="R40" t="n">
-        <v>7043822</v>
+        <v>7043954</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4949,7 +4820,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4959,12 +4830,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4979,22 +4845,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132926421</v>
+        <v>132919816</v>
       </c>
       <c r="B41" t="n">
-        <v>57958</v>
+        <v>80488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5002,39 +4868,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582415</v>
+        <v>582579</v>
       </c>
       <c r="R41" t="n">
-        <v>7043878</v>
+        <v>7043890</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5066,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5076,12 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5108,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132919076</v>
+        <v>132920807</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,39 +4975,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582558</v>
+        <v>582487</v>
       </c>
       <c r="R42" t="n">
-        <v>7043820</v>
+        <v>7043925</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5183,7 +5034,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5193,12 +5044,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5225,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132920570</v>
+        <v>132926073</v>
       </c>
       <c r="B43" t="n">
-        <v>79334</v>
+        <v>80488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5236,21 +5082,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5260,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582496</v>
+        <v>582376</v>
       </c>
       <c r="R43" t="n">
-        <v>7043918</v>
+        <v>7043830</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5295,7 +5141,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5305,7 +5151,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5332,32 +5178,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132926154</v>
+        <v>132928145</v>
       </c>
       <c r="B44" t="n">
-        <v>92300</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5367,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582384</v>
+        <v>582574</v>
       </c>
       <c r="R44" t="n">
-        <v>7043861</v>
+        <v>7043941</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5402,7 +5248,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5412,7 +5258,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5439,10 +5285,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132919360</v>
+        <v>132928237</v>
       </c>
       <c r="B45" t="n">
-        <v>79334</v>
+        <v>80488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,21 +5296,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5474,10 +5320,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582533</v>
+        <v>582565</v>
       </c>
       <c r="R45" t="n">
-        <v>7043840</v>
+        <v>7043970</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5509,7 +5355,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5519,7 +5365,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5546,45 +5392,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132927050</v>
+        <v>132924572</v>
       </c>
       <c r="B46" t="n">
-        <v>79334</v>
+        <v>57972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582494</v>
+        <v>582219</v>
       </c>
       <c r="R46" t="n">
-        <v>7043853</v>
+        <v>7043925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5616,7 +5467,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5626,7 +5477,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5653,10 +5504,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132925842</v>
+        <v>132919032</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5535,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5693,13 +5544,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582336</v>
+        <v>582546</v>
       </c>
       <c r="R47" t="n">
-        <v>7043843</v>
+        <v>7043836</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5728,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5738,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5758,49 +5609,50 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132925338</v>
+        <v>132919043</v>
       </c>
       <c r="B48" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5809,13 +5661,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582282</v>
+        <v>582561</v>
       </c>
       <c r="R48" t="n">
-        <v>7043849</v>
+        <v>7043822</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5844,7 +5696,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5854,7 +5706,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5869,22 +5726,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132926110</v>
+        <v>132919076</v>
       </c>
       <c r="B49" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5769,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5921,10 +5778,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582398</v>
+        <v>582558</v>
       </c>
       <c r="R49" t="n">
-        <v>7043860</v>
+        <v>7043820</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5956,7 +5813,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5966,7 +5823,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -5998,10 +5855,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132920621</v>
+        <v>132919337</v>
       </c>
       <c r="B50" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,37 +5866,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>582501</v>
+        <v>582540</v>
       </c>
       <c r="R50" t="n">
-        <v>7043923</v>
+        <v>7043843</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6068,7 +5930,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6078,7 +5940,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,22 +5960,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132919337</v>
+        <v>132919519</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6136,7 +6003,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6145,13 +6012,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>582540</v>
+        <v>582548</v>
       </c>
       <c r="R51" t="n">
-        <v>7043843</v>
+        <v>7043854</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6180,7 +6047,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6190,7 +6057,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6210,22 +6077,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132926178</v>
+        <v>132920257</v>
       </c>
       <c r="B52" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,7 +6120,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6262,10 +6129,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582395</v>
+        <v>582548</v>
       </c>
       <c r="R52" t="n">
-        <v>7043859</v>
+        <v>7043881</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6297,7 +6164,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6307,7 +6174,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6339,10 +6206,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132926237</v>
+        <v>132920331</v>
       </c>
       <c r="B53" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6370,7 +6237,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6379,13 +6246,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582399</v>
+        <v>582528</v>
       </c>
       <c r="R53" t="n">
-        <v>7043854</v>
+        <v>7043891</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6414,7 +6281,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6424,7 +6291,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6444,22 +6311,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132920535</v>
+        <v>132920433</v>
       </c>
       <c r="B54" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6467,37 +6334,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582516</v>
+        <v>582522</v>
       </c>
       <c r="R54" t="n">
-        <v>7043923</v>
+        <v>7043904</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6526,7 +6398,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6536,7 +6408,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6551,22 +6428,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132924903</v>
+        <v>132922007</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6574,37 +6451,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582175</v>
+        <v>582415</v>
       </c>
       <c r="R55" t="n">
-        <v>7043894</v>
+        <v>7043917</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6633,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6643,7 +6525,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6658,22 +6545,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132926960</v>
+        <v>132923635</v>
       </c>
       <c r="B56" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6681,34 +6568,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582484</v>
+        <v>582306</v>
       </c>
       <c r="R56" t="n">
-        <v>7043864</v>
+        <v>7043991</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6740,7 +6632,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6750,7 +6642,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6777,10 +6674,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132928234</v>
+        <v>132924726</v>
       </c>
       <c r="B57" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6788,34 +6685,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582566</v>
+        <v>582191</v>
       </c>
       <c r="R57" t="n">
-        <v>7043963</v>
+        <v>7043924</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6847,7 +6749,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6857,7 +6759,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6884,10 +6791,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132927484</v>
+        <v>132924803</v>
       </c>
       <c r="B58" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6915,7 +6822,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6924,13 +6831,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582555</v>
+        <v>582184</v>
       </c>
       <c r="R58" t="n">
-        <v>7043817</v>
+        <v>7043908</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6959,7 +6866,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6969,7 +6876,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6989,22 +6896,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132920331</v>
+        <v>132925090</v>
       </c>
       <c r="B59" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7041,13 +6948,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582528</v>
+        <v>582199</v>
       </c>
       <c r="R59" t="n">
-        <v>7043891</v>
+        <v>7043873</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7076,7 +6983,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7086,7 +6993,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7106,22 +7013,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132925942</v>
+        <v>132925210</v>
       </c>
       <c r="B60" t="n">
-        <v>91949</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7129,34 +7036,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>582341</v>
+        <v>582246</v>
       </c>
       <c r="R60" t="n">
-        <v>7043851</v>
+        <v>7043866</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7188,7 +7100,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7198,7 +7110,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7225,37 +7142,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132926466</v>
+        <v>132925219</v>
       </c>
       <c r="B61" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7264,10 +7182,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582411</v>
+        <v>582236</v>
       </c>
       <c r="R61" t="n">
-        <v>7043872</v>
+        <v>7043854</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7299,7 +7217,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7309,7 +7227,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7324,22 +7247,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132926094</v>
+        <v>132925440</v>
       </c>
       <c r="B62" t="n">
-        <v>92227</v>
+        <v>57975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7347,21 +7270,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7371,10 +7294,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582388</v>
+        <v>582314</v>
       </c>
       <c r="R62" t="n">
-        <v>7043864</v>
+        <v>7043846</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7406,7 +7329,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7416,7 +7339,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7443,10 +7371,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132926171</v>
+        <v>132925842</v>
       </c>
       <c r="B63" t="n">
-        <v>92227</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7454,37 +7382,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582386</v>
+        <v>582336</v>
       </c>
       <c r="R63" t="n">
-        <v>7043846</v>
+        <v>7043843</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7513,7 +7446,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7523,7 +7456,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7538,22 +7476,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132925307</v>
+        <v>132926110</v>
       </c>
       <c r="B64" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7561,37 +7499,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582282</v>
+        <v>582398</v>
       </c>
       <c r="R64" t="n">
-        <v>7043846</v>
+        <v>7043860</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7620,7 +7563,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7630,7 +7573,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7645,22 +7593,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132920807</v>
+        <v>132926178</v>
       </c>
       <c r="B65" t="n">
-        <v>80439</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7668,34 +7616,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582487</v>
+        <v>582395</v>
       </c>
       <c r="R65" t="n">
-        <v>7043925</v>
+        <v>7043859</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7727,7 +7680,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7737,7 +7690,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7764,10 +7722,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132928237</v>
+        <v>132926237</v>
       </c>
       <c r="B66" t="n">
-        <v>80439</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7775,34 +7733,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582565</v>
+        <v>582399</v>
       </c>
       <c r="R66" t="n">
-        <v>7043970</v>
+        <v>7043854</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7834,7 +7797,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7844,7 +7807,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7871,10 +7839,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132920257</v>
+        <v>132926412</v>
       </c>
       <c r="B67" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7911,10 +7879,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>582548</v>
+        <v>582422</v>
       </c>
       <c r="R67" t="n">
-        <v>7043881</v>
+        <v>7043879</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7946,7 +7914,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7956,7 +7924,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -7988,10 +7956,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132919519</v>
+        <v>132926421</v>
       </c>
       <c r="B68" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8019,7 +7987,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8028,10 +7996,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>582548</v>
+        <v>582415</v>
       </c>
       <c r="R68" t="n">
-        <v>7043854</v>
+        <v>7043878</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8063,7 +8031,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8073,7 +8041,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8105,37 +8073,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132921030</v>
+        <v>132926854</v>
       </c>
       <c r="B69" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8144,13 +8113,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>582465</v>
+        <v>582450</v>
       </c>
       <c r="R69" t="n">
-        <v>7043920</v>
+        <v>7043889</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8179,7 +8148,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8189,7 +8158,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8204,49 +8178,50 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132920457</v>
+        <v>132927178</v>
       </c>
       <c r="B70" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8255,10 +8230,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>582512</v>
+        <v>582507</v>
       </c>
       <c r="R70" t="n">
-        <v>7043909</v>
+        <v>7043843</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8290,7 +8265,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8300,7 +8275,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8327,10 +8307,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132920433</v>
+        <v>132927409</v>
       </c>
       <c r="B71" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,10 +8347,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>582522</v>
+        <v>582554</v>
       </c>
       <c r="R71" t="n">
-        <v>7043904</v>
+        <v>7043810</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8402,7 +8382,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8412,7 +8392,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8444,10 +8424,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132925210</v>
+        <v>132927484</v>
       </c>
       <c r="B72" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8475,7 +8455,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8484,13 +8464,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>582246</v>
+        <v>582555</v>
       </c>
       <c r="R72" t="n">
-        <v>7043866</v>
+        <v>7043817</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8519,7 +8499,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8529,7 +8509,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8549,39 +8529,39 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132924803</v>
+        <v>132920346</v>
       </c>
       <c r="B73" t="n">
-        <v>57958</v>
+        <v>57153</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8592,7 +8572,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8601,13 +8581,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>582184</v>
+        <v>582529</v>
       </c>
       <c r="R73" t="n">
-        <v>7043908</v>
+        <v>7043897</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8636,7 +8616,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8646,12 +8626,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8666,57 +8641,61 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132921934</v>
+        <v>132918849</v>
       </c>
       <c r="B74" t="n">
-        <v>79334</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>582424</v>
+        <v>582572</v>
       </c>
       <c r="R74" t="n">
-        <v>7043909</v>
+        <v>7043799</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8748,7 +8727,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8758,7 +8737,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8785,10 +8764,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132925868</v>
+        <v>132919891</v>
       </c>
       <c r="B75" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8815,12 +8794,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8829,13 +8803,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>582341</v>
+        <v>582574</v>
       </c>
       <c r="R75" t="n">
-        <v>7043829</v>
+        <v>7043884</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8864,7 +8838,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8874,7 +8848,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8889,15 +8863,1705 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132920457</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>582512</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7043909</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132921030</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>582465</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7043920</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132923147</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>582359</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7043899</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132923334</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>582317</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7043947</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AX79" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132923509</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>582304</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7043964</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132924479</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>582214</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7043984</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132924664</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>582220</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7043925</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132924740</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>582171</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7043917</v>
+      </c>
+      <c r="S83" t="n">
+        <v>20</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132925040</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>582178</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7043860</v>
+      </c>
+      <c r="S84" t="n">
+        <v>20</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132925338</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>582282</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7043849</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132925868</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>582341</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7043829</v>
+      </c>
+      <c r="S86" t="n">
+        <v>20</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132926033</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>582361</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7043841</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132926466</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>582411</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7043872</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132928312</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>582582</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7043957</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132929699</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>582614</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7043883</v>
+      </c>
+      <c r="S90" t="n">
+        <v>20</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14787-2026 artfynd.xlsx
+++ b/artfynd/A 14787-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925650</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925538</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926094</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920535</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132923551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924276</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925262</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925307</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2072,6 +2137,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926159</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926678</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928047</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926766</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2500,6 +2585,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926154</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2607,6 +2697,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926776</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2714,6 +2809,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928275</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2821,6 +2921,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920065</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2928,6 +3033,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925942</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3035,6 +3145,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919070</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3142,6 +3257,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919360</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3249,6 +3369,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920356</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3356,6 +3481,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920570</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3463,6 +3593,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921934</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3570,6 +3705,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132922379</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3677,6 +3817,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132922973</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3784,6 +3929,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132923528</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3891,6 +4041,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924051</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3998,6 +4153,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924527</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4105,6 +4265,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924676</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4212,6 +4377,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924903</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4319,6 +4489,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925222</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4426,6 +4601,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925362</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4533,6 +4713,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926960</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4640,6 +4825,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132927050</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4747,6 +4937,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928234</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4854,6 +5049,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928381</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4961,6 +5161,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919816</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5068,6 +5273,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920807</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5175,6 +5385,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926073</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5282,6 +5497,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928145</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5389,6 +5609,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928237</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5501,6 +5726,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924572</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5618,6 +5848,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919032</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5735,6 +5970,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919043</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5852,6 +6092,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919076</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5969,6 +6214,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919337</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6086,6 +6336,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919519</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6203,6 +6458,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920257</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6320,6 +6580,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920331</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6437,6 +6702,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920433</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6554,6 +6824,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132922007</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6671,6 +6946,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132923635</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6788,6 +7068,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924726</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6905,6 +7190,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924803</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7022,6 +7312,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925090</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7139,6 +7434,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925210</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7256,6 +7556,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925219</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7368,6 +7673,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925440</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7485,6 +7795,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925842</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7602,6 +7917,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926110</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7719,6 +8039,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926178</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7836,6 +8161,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926237</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7953,6 +8283,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926412</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8070,6 +8405,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926421</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8187,6 +8527,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926854</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8304,6 +8649,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132927178</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8421,6 +8771,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132927409</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8538,6 +8893,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132927484</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8650,6 +9010,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920346</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8761,6 +9126,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918849</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8872,6 +9242,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919891</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8983,6 +9358,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920457</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9094,6 +9474,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921030</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9205,6 +9590,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132923147</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9321,6 +9711,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132923334</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9432,6 +9827,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132923509</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9543,6 +9943,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924479</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9654,6 +10059,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924664</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9770,6 +10180,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132924740</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9886,6 +10301,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925040</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9997,6 +10417,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925338</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10113,6 +10538,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132925868</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10224,6 +10654,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926033</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10335,6 +10770,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132926466</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10446,6 +10886,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928312</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10562,8 +11007,104 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929699</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>